--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486485_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486485_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8958</v>
+        <v>5.7841</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5376</v>
+        <v>4.3312</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3582</v>
+        <v>1.4529</v>
       </c>
       <c r="G2" t="n">
-        <v>1.0874</v>
+        <v>8.885300000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2736</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>1.361</v>
+        <v>8.261900000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7777</v>
+        <v>9.311</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1547</v>
+        <v>0.6268</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9324</v>
+        <v>8.684200000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6902</v>
+        <v>-0.4257</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1188</v>
+        <v>-0.0033</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5714</v>
+        <v>-0.4224</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6525</v>
+        <v>-3.6976</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0875</v>
+        <v>-5.4377</v>
       </c>
       <c r="R2" t="n">
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6354</v>
+        <v>0.7916</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1971</v>
+        <v>0.4579</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4383</v>
+        <v>0.3338</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5204</v>
+        <v>-0.1952</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6504</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5557</v>
+        <v>4.4287</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2569</v>
+        <v>3.7179</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2988</v>
+        <v>0.7109</v>
       </c>
       <c r="G3" t="n">
-        <v>8.885300000000001</v>
+        <v>1.0874</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6235000000000001</v>
+        <v>-0.2736</v>
       </c>
       <c r="I3" t="n">
-        <v>8.261900000000001</v>
+        <v>1.361</v>
       </c>
       <c r="J3" t="n">
-        <v>9.311</v>
+        <v>1.7777</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6268</v>
+        <v>-0.1547</v>
       </c>
       <c r="L3" t="n">
-        <v>8.684200000000001</v>
+        <v>1.9324</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4257</v>
+        <v>-0.6902</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0033</v>
+        <v>-0.1188</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4224</v>
+        <v>-0.5714</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.6976</v>
+        <v>0.6525</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.4377</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
         <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4368</v>
+        <v>1.1683</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6165</v>
+        <v>0.3773</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1796</v>
+        <v>0.791</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1952</v>
+        <v>1.5204</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.6504</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4502</v>
+        <v>2.2124</v>
       </c>
       <c r="E4" t="n">
-        <v>1.934</v>
+        <v>1.5536</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5162</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1977</v>
+        <v>1.32</v>
       </c>
       <c r="H4" t="n">
-        <v>1.773</v>
+        <v>0.5534</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5754</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6218</v>
+        <v>2.9577</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6274</v>
+        <v>1.0037</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9945000000000001</v>
+        <v>1.9539</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4241</v>
+        <v>-1.6377</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1457</v>
+        <v>-0.4504</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5698</v>
+        <v>-1.1873</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1872</v>
+        <v>0.545</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2268</v>
+        <v>0.0108</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0395</v>
+        <v>0.5341</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9347</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7395</v>
+        <v>0.7602</v>
       </c>
       <c r="X4" t="n">
         <v>-0.1952</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>D. DE SOUSA ANJO BRITO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6331</v>
+        <v>2.1701</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7893</v>
+        <v>1.8651</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8437</v>
+        <v>0.3051</v>
       </c>
       <c r="G5" t="n">
-        <v>1.32</v>
+        <v>2.4779</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5534</v>
+        <v>0.4531</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7665999999999999</v>
+        <v>2.0248</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9577</v>
+        <v>4.5961</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0037</v>
+        <v>0.7879</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9539</v>
+        <v>3.8082</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6377</v>
+        <v>-2.1182</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4504</v>
+        <v>-0.3348</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1873</v>
+        <v>-1.7834</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>-4.3501</v>
       </c>
       <c r="R5" t="n">
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0344</v>
+        <v>1.15</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.4891</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7191</v>
+        <v>0.6609</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.9347</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7602</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
         <v>-0.1952</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. DE SOUSA ANJO BRITO</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6178</v>
+        <v>1.6536</v>
       </c>
       <c r="E6" t="n">
-        <v>1.436</v>
+        <v>0.7984</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1818</v>
+        <v>0.8552</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4779</v>
+        <v>1.1977</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4531</v>
+        <v>1.773</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0248</v>
+        <v>-0.5754</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5961</v>
+        <v>2.6218</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7879</v>
+        <v>1.6274</v>
       </c>
       <c r="L6" t="n">
-        <v>3.8082</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1182</v>
+        <v>-1.4241</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3348</v>
+        <v>0.1457</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7834</v>
+        <v>-1.5698</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.3926</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.3501</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5977</v>
+        <v>1.3907</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0601</v>
+        <v>1.0911</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5376</v>
+        <v>0.2995</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9347</v>
+        <v>-0.9347</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="X6" t="n">
         <v>-0.1952</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3081</v>
+        <v>0.3362</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2616</v>
+        <v>0.6595</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0465</v>
+        <v>-0.3234</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4594</v>
@@ -1000,13 +1000,13 @@
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>1.985</v>
+        <v>1.013</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0106</v>
+        <v>0.4086</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.6044</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5972</v>
+        <v>-0.5172</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3584</v>
+        <v>1.3152</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9556</v>
+        <v>-1.8324</v>
       </c>
       <c r="G8" t="n">
         <v>0.644</v>
@@ -1078,13 +1078,13 @@
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1062</v>
+        <v>0.1863</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4026</v>
+        <v>0.3593</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2963</v>
+        <v>-0.173</v>
       </c>
       <c r="V8" t="n">
         <v>-1.13</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. MUNNINGS</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1015</v>
+        <v>-0.8189</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6185</v>
+        <v>-0.0476</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.72</v>
+        <v>-0.7713</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5869</v>
+        <v>-3.9005</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6324</v>
+        <v>-0.6692</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.2193</v>
+        <v>-3.2313</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0002</v>
+        <v>-1.3687</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9671999999999999</v>
+        <v>-0.0698</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9674</v>
+        <v>-1.2989</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5867</v>
+        <v>-2.5318</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3348</v>
+        <v>-0.5994</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2519</v>
+        <v>-1.9324</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5278</v>
+        <v>0.6465</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6187</v>
+        <v>0.1911</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.4554</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.13</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>T. MUNNINGS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.695</v>
+        <v>-1.4955</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9237</v>
+        <v>-0.2071</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7713</v>
+        <v>-1.2885</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.9005</v>
+        <v>-2.5869</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6692</v>
+        <v>0.6324</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.2313</v>
+        <v>-3.2193</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3687</v>
+        <v>-1.0002</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0698</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2989</v>
+        <v>-1.9674</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5318</v>
+        <v>-1.5867</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5994</v>
+        <v>-0.3348</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.9324</v>
+        <v>-1.2519</v>
       </c>
       <c r="P10" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2295</v>
+        <v>1.1338</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.7931</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4554</v>
+        <v>0.3407</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3667</v>
+        <v>-4.6834</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9475</v>
+        <v>-4.295</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4192</v>
+        <v>-0.3884</v>
       </c>
       <c r="G11" t="n">
         <v>-4.5858</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1285</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.0324</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5565</v>
+        <v>0.5873</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.7003</v>
+        <v>9.0701</v>
       </c>
       <c r="E12" t="n">
-        <v>8.321099999999999</v>
+        <v>9.6912</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6209000000000006</v>
+        <v>-0.6211</v>
       </c>
       <c r="G12" t="n">
         <v>4.079700000000002</v>
@@ -1360,7 +1360,7 @@
         <v>-0.9125000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>4.992200000000002</v>
+        <v>4.992200000000001</v>
       </c>
       <c r="J12" t="n">
         <v>20.1898</v>
@@ -1390,19 +1390,19 @@
         <v>15.2255</v>
       </c>
       <c r="S12" t="n">
-        <v>7.2101</v>
+        <v>8.580099999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7759</v>
+        <v>4.1459</v>
       </c>
       <c r="U12" t="n">
         <v>4.4341</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7601999999999999</v>
+        <v>0.7601999999999998</v>
       </c>
       <c r="W12" t="n">
-        <v>4.9311</v>
+        <v>4.931099999999999</v>
       </c>
       <c r="X12" t="n">
         <v>-4.1708</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4443</v>
+        <v>5.7179</v>
       </c>
       <c r="E13" t="n">
-        <v>5.133</v>
+        <v>5.4683</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3113</v>
+        <v>0.2496</v>
       </c>
       <c r="G13" t="n">
         <v>2.0935</v>
@@ -1468,13 +1468,13 @@
         <v>3.4801</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3017</v>
+        <v>-1.0281</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0719</v>
+        <v>-0.7366</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2298</v>
+        <v>-0.2914</v>
       </c>
       <c r="V13" t="n">
         <v>2.2599</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5425</v>
+        <v>4.1726</v>
       </c>
       <c r="E14" t="n">
         <v>3.2228</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3196</v>
+        <v>0.9497</v>
       </c>
       <c r="G14" t="n">
         <v>3.9791</v>
@@ -1546,13 +1546,13 @@
         <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5242</v>
+        <v>-0.8941</v>
       </c>
       <c r="T14" t="n">
         <v>-0.7413999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2173</v>
+        <v>-0.1526</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3819</v>
+        <v>3.7402</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7072</v>
+        <v>3.819</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3253</v>
+        <v>-0.0788</v>
       </c>
       <c r="G15" t="n">
         <v>4.4985</v>
@@ -1624,13 +1624,13 @@
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7691</v>
+        <v>-1.4108</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8099</v>
+        <v>-0.6982</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9592000000000001</v>
+        <v>-0.7126</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3094</v>
+        <v>-0.2786</v>
       </c>
       <c r="E16" t="n">
         <v>-0.149</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1604</v>
+        <v>-0.1296</v>
       </c>
       <c r="G16" t="n">
         <v>-0.193</v>
@@ -1702,13 +1702,13 @@
         <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.334</v>
+        <v>-0.3031</v>
       </c>
       <c r="T16" t="n">
         <v>-0.2055</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4535</v>
+        <v>-0.6269</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8114</v>
+        <v>0.6997</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2649</v>
+        <v>-1.3265</v>
       </c>
       <c r="G17" t="n">
         <v>-1.9094</v>
@@ -1780,13 +1780,13 @@
         <v>3.6976</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9796</v>
+        <v>-1.153</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5323</v>
+        <v>-0.6441</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4473</v>
+        <v>-0.5089</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1745</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7996</v>
+        <v>-1.7688</v>
       </c>
       <c r="E18" t="n">
         <v>-0.149</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6506</v>
+        <v>-1.6198</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5755</v>
@@ -1858,13 +1858,13 @@
         <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1164</v>
+        <v>-0.0856</v>
       </c>
       <c r="T18" t="n">
         <v>-0.2055</v>
       </c>
       <c r="U18" t="n">
-        <v>0.089</v>
+        <v>0.1199</v>
       </c>
       <c r="V18" t="n">
         <v>-1.3252</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8497</v>
+        <v>-2.7149</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8635</v>
+        <v>-0.9752</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9862</v>
+        <v>-1.7396</v>
       </c>
       <c r="G19" t="n">
         <v>-2.3494</v>
@@ -1936,13 +1936,13 @@
         <v>2.8276</v>
       </c>
       <c r="S19" t="n">
-        <v>-1</v>
+        <v>-0.8652</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2584</v>
+        <v>-0.3701</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7417</v>
+        <v>-0.4951</v>
       </c>
       <c r="V19" t="n">
         <v>0.9347</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5179</v>
+        <v>-3.7452</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.3169</v>
+        <v>-3.2052</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.201</v>
+        <v>-0.5401</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4646</v>
@@ -2014,13 +2014,13 @@
         <v>2.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.8679</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7294</v>
+        <v>-0.6177</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0888</v>
+        <v>-0.2503</v>
       </c>
       <c r="V20" t="n">
         <v>-1.3252</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.166</v>
+        <v>-4.2354</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6864</v>
+        <v>-2.9099</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4795</v>
+        <v>-1.3254</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4347</v>
@@ -2092,13 +2092,13 @@
         <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2962</v>
+        <v>-0.3656</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.2319</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2878</v>
+        <v>-0.1337</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.9727</v>
+        <v>-7.9611</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.0886</v>
+        <v>-5.2003</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8841</v>
+        <v>-2.7608</v>
       </c>
       <c r="G22" t="n">
         <v>-5.7244</v>
@@ -2170,13 +2170,13 @@
         <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2483</v>
+        <v>-0.2367</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1286</v>
+        <v>0.0168</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3769</v>
+        <v>-0.2536</v>
       </c>
       <c r="V22" t="n">
         <v>-1.13</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.700099999999999</v>
+        <v>-7.700200000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6210000000000013</v>
+        <v>0.6212</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.321099999999999</v>
+        <v>-8.321300000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-4.0799</v>
@@ -2248,13 +2248,13 @@
         <v>19.5757</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.210100000000001</v>
+        <v>-7.210099999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.4341</v>
+        <v>-4.434200000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.7761</v>
+        <v>-2.7759</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7602999999999995</v>
